--- a/Deliverables/12S/regions/sbering/ADFG_12s_sbering_speciesxsamples.xlsx
+++ b/Deliverables/12S/regions/sbering/ADFG_12s_sbering_speciesxsamples.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -388,27 +388,27 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Boreogadus saida</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Myoxocephalus spp.</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Ammodytes hexapterus</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lepidopsetta spp.</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Hypomesus olidus</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Ammodytes hexapterus</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Myoxocephalus spp.</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Boreogadus saida</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Lepidopsetta spp.</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -434,19 +434,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>20531</v>
+        <v>20443</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>19940</v>
+        <v>19936</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>67</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -458,7 +458,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>68</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>35542</v>
+        <v>35541</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -494,10 +494,10 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>567</v>
       </c>
       <c r="I3">
-        <v>567</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>26316</v>
+        <v>26315</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -539,10 +539,10 @@
         <v>0</v>
       </c>
       <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>31</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -584,10 +584,10 @@
         <v>0</v>
       </c>
       <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>23</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>14299</v>
+        <v>14298</v>
       </c>
       <c r="D13">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1038</v>
@@ -944,10 +944,10 @@
         <v>0</v>
       </c>
       <c r="H13">
+        <v>0</v>
+      </c>
+      <c r="I13">
         <v>64</v>
-      </c>
-      <c r="I13">
-        <v>0</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>6509</v>
+        <v>6514</v>
       </c>
       <c r="D14">
         <v>4102</v>
@@ -986,7 +986,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>199</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -995,7 +995,7 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>199</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
@@ -1064,19 +1064,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>546915</v>
+        <v>551290</v>
       </c>
       <c r="D16">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>706013</v>
+        <v>710790</v>
       </c>
       <c r="F16">
-        <v>95083</v>
+        <v>95129</v>
       </c>
       <c r="G16">
-        <v>37160</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>37255</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1124,10 +1124,10 @@
         <v>0</v>
       </c>
       <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>35</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -1169,10 +1169,10 @@
         <v>0</v>
       </c>
       <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <v>1693</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -1214,16 +1214,16 @@
         <v>0</v>
       </c>
       <c r="H19">
+        <v>2060</v>
+      </c>
+      <c r="I19">
         <v>11</v>
       </c>
-      <c r="I19">
-        <v>2060</v>
-      </c>
       <c r="J19">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="K19">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -1256,7 +1256,7 @@
         <v>0</v>
       </c>
       <c r="G20">
-        <v>937</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -1268,13 +1268,58 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>941</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
         <v>206</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WADE-003-184</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PH10HB027</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>577</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1284,7 +1329,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1320,27 +1365,27 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>Boreogadus saida</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Myoxocephalus spp.</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Ammodytes hexapterus</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Lepidopsetta spp.</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>Hypomesus olidus</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Ammodytes hexapterus</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Myoxocephalus spp.</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>Boreogadus saida</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Lepidopsetta spp.</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
@@ -1366,19 +1411,19 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.50646</v>
+        <v>0.50543</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.49188</v>
+        <v>0.49289</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0.00165</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1390,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0</v>
+        <v>0.00168</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1411,13 +1456,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.97662</v>
+        <v>0.97619</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.0078</v>
+        <v>0.008240000000000001</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1426,10 +1471,10 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0</v>
+        <v>0.01557</v>
       </c>
       <c r="I3">
-        <v>0.01558</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0</v>
@@ -1471,10 +1516,10 @@
         <v>0</v>
       </c>
       <c r="H4">
+        <v>0</v>
+      </c>
+      <c r="I4">
         <v>0.00118</v>
-      </c>
-      <c r="I4">
-        <v>0</v>
       </c>
       <c r="J4">
         <v>0</v>
@@ -1516,10 +1561,10 @@
         <v>0</v>
       </c>
       <c r="H5">
+        <v>0</v>
+      </c>
+      <c r="I5">
         <v>0.01492</v>
-      </c>
-      <c r="I5">
-        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -1861,13 +1906,13 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.9252</v>
+        <v>0.92844</v>
       </c>
       <c r="D13">
-        <v>0.00349</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0.06716</v>
+        <v>0.0674</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1876,10 +1921,10 @@
         <v>0</v>
       </c>
       <c r="H13">
-        <v>0.00414</v>
+        <v>0</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>0.00416</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1906,10 +1951,10 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.57909</v>
+        <v>0.57928</v>
       </c>
       <c r="D14">
-        <v>0.36495</v>
+        <v>0.36478</v>
       </c>
       <c r="E14">
         <v>0.00427</v>
@@ -1918,7 +1963,7 @@
         <v>0</v>
       </c>
       <c r="G14">
-        <v>0</v>
+        <v>0.0177</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -1927,13 +1972,13 @@
         <v>0</v>
       </c>
       <c r="J14">
-        <v>0.0177</v>
+        <v>0</v>
       </c>
       <c r="K14">
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0.03399</v>
+        <v>0.03397</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -1996,19 +2041,19 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.39476</v>
+        <v>0.39534</v>
       </c>
       <c r="D16">
-        <v>0.00019</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0.5096000000000001</v>
+        <v>0.50972</v>
       </c>
       <c r="F16">
-        <v>0.06863</v>
+        <v>0.06822</v>
       </c>
       <c r="G16">
-        <v>0.02682</v>
+        <v>0</v>
       </c>
       <c r="H16">
         <v>0</v>
@@ -2020,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0</v>
+        <v>0.02672</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2056,10 +2101,10 @@
         <v>0</v>
       </c>
       <c r="H17">
+        <v>0</v>
+      </c>
+      <c r="I17">
         <v>0.00113</v>
-      </c>
-      <c r="I17">
-        <v>0</v>
       </c>
       <c r="J17">
         <v>0</v>
@@ -2101,10 +2146,10 @@
         <v>0</v>
       </c>
       <c r="H18">
+        <v>0</v>
+      </c>
+      <c r="I18">
         <v>0.12918</v>
-      </c>
-      <c r="I18">
-        <v>0</v>
       </c>
       <c r="J18">
         <v>0</v>
@@ -2146,16 +2191,16 @@
         <v>0</v>
       </c>
       <c r="H19">
+        <v>0.90351</v>
+      </c>
+      <c r="I19">
         <v>0.00482</v>
       </c>
-      <c r="I19">
-        <v>0.90351</v>
-      </c>
       <c r="J19">
-        <v>0</v>
+        <v>0.02105</v>
       </c>
       <c r="K19">
-        <v>0.02105</v>
+        <v>0</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -2176,19 +2221,19 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.71454</v>
+        <v>0.7139</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.02935</v>
+        <v>0.02933</v>
       </c>
       <c r="F20">
         <v>0</v>
       </c>
       <c r="G20">
-        <v>0.20995</v>
+        <v>0</v>
       </c>
       <c r="H20">
         <v>0</v>
@@ -2200,13 +2245,58 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>0.21066</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0.04616</v>
+        <v>0.04612</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>WADE-003-184</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>PH10HB027</t>
+        </is>
+      </c>
+      <c r="C21">
+        <v>1</v>
+      </c>
+      <c r="D21">
+        <v>0</v>
+      </c>
+      <c r="E21">
+        <v>0</v>
+      </c>
+      <c r="F21">
+        <v>0</v>
+      </c>
+      <c r="G21">
+        <v>0</v>
+      </c>
+      <c r="H21">
+        <v>0</v>
+      </c>
+      <c r="I21">
+        <v>0</v>
+      </c>
+      <c r="J21">
+        <v>0</v>
+      </c>
+      <c r="K21">
+        <v>0</v>
+      </c>
+      <c r="L21">
+        <v>0</v>
+      </c>
+      <c r="M21">
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Deliverables/12S/regions/sbering/ADFG_12s_sbering_speciesxsamples.xlsx
+++ b/Deliverables/12S/regions/sbering/ADFG_12s_sbering_speciesxsamples.xlsx
@@ -434,13 +434,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>20443</v>
+        <v>20531</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>19936</v>
+        <v>19940</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -458,7 +458,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>35541</v>
+        <v>35542</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>26315</v>
+        <v>26316</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>14298</v>
+        <v>14299</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>54</v>
       </c>
       <c r="E13">
         <v>1038</v>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>6514</v>
+        <v>6509</v>
       </c>
       <c r="D14">
         <v>4102</v>
@@ -1064,16 +1064,16 @@
         </is>
       </c>
       <c r="C16">
-        <v>551290</v>
+        <v>546915</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>268</v>
       </c>
       <c r="E16">
-        <v>710790</v>
+        <v>706013</v>
       </c>
       <c r="F16">
-        <v>95129</v>
+        <v>95083</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>37255</v>
+        <v>37160</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>941</v>
+        <v>937</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1411,13 +1411,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.50543</v>
+        <v>0.50646</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.49289</v>
+        <v>0.49188</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0.00168</v>
+        <v>0.00165</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.97619</v>
+        <v>0.97662</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.008240000000000001</v>
+        <v>0.0078</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0.01557</v>
+        <v>0.01558</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.92844</v>
+        <v>0.9252</v>
       </c>
       <c r="D13">
-        <v>0</v>
+        <v>0.00349</v>
       </c>
       <c r="E13">
-        <v>0.0674</v>
+        <v>0.06716</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1924,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.00416</v>
+        <v>0.00414</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.57928</v>
+        <v>0.57909</v>
       </c>
       <c r="D14">
-        <v>0.36478</v>
+        <v>0.36495</v>
       </c>
       <c r="E14">
         <v>0.00427</v>
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0.03397</v>
+        <v>0.03399</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.39534</v>
+        <v>0.39476</v>
       </c>
       <c r="D16">
-        <v>0</v>
+        <v>0.00019</v>
       </c>
       <c r="E16">
-        <v>0.50972</v>
+        <v>0.5096000000000001</v>
       </c>
       <c r="F16">
-        <v>0.06822</v>
+        <v>0.06863</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0.02672</v>
+        <v>0.02682</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.7139</v>
+        <v>0.71454</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.02933</v>
+        <v>0.02935</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -2245,13 +2245,13 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0.21066</v>
+        <v>0.20995</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0.04612</v>
+        <v>0.04616</v>
       </c>
     </row>
     <row r="21">

--- a/Deliverables/12S/regions/sbering/ADFG_12s_sbering_speciesxsamples.xlsx
+++ b/Deliverables/12S/regions/sbering/ADFG_12s_sbering_speciesxsamples.xlsx
@@ -434,13 +434,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>20531</v>
+        <v>20443</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>19940</v>
+        <v>19936</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -458,7 +458,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -479,13 +479,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>35542</v>
+        <v>35541</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>284</v>
+        <v>300</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="C4">
-        <v>26316</v>
+        <v>26315</v>
       </c>
       <c r="D4">
         <v>0</v>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="C13">
-        <v>14299</v>
+        <v>14298</v>
       </c>
       <c r="D13">
-        <v>54</v>
+        <v>0</v>
       </c>
       <c r="E13">
         <v>1038</v>
@@ -974,7 +974,7 @@
         </is>
       </c>
       <c r="C14">
-        <v>6509</v>
+        <v>6514</v>
       </c>
       <c r="D14">
         <v>4102</v>
@@ -1064,16 +1064,16 @@
         </is>
       </c>
       <c r="C16">
-        <v>546915</v>
+        <v>551290</v>
       </c>
       <c r="D16">
-        <v>268</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>706013</v>
+        <v>710790</v>
       </c>
       <c r="F16">
-        <v>95083</v>
+        <v>95129</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -1088,7 +1088,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>37160</v>
+        <v>37255</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -1268,7 +1268,7 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -1411,13 +1411,13 @@
         </is>
       </c>
       <c r="C2">
-        <v>0.50646</v>
+        <v>0.50543</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0.49188</v>
+        <v>0.49289</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -1435,7 +1435,7 @@
         <v>0</v>
       </c>
       <c r="K2">
-        <v>0.00165</v>
+        <v>0.00168</v>
       </c>
       <c r="L2">
         <v>0</v>
@@ -1456,13 +1456,13 @@
         </is>
       </c>
       <c r="C3">
-        <v>0.97662</v>
+        <v>0.97619</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0.0078</v>
+        <v>0.008240000000000001</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -1471,7 +1471,7 @@
         <v>0</v>
       </c>
       <c r="H3">
-        <v>0.01558</v>
+        <v>0.01557</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -1906,13 +1906,13 @@
         </is>
       </c>
       <c r="C13">
-        <v>0.9252</v>
+        <v>0.92844</v>
       </c>
       <c r="D13">
-        <v>0.00349</v>
+        <v>0</v>
       </c>
       <c r="E13">
-        <v>0.06716</v>
+        <v>0.0674</v>
       </c>
       <c r="F13">
         <v>0</v>
@@ -1924,7 +1924,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>0.00414</v>
+        <v>0.00416</v>
       </c>
       <c r="J13">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         </is>
       </c>
       <c r="C14">
-        <v>0.57909</v>
+        <v>0.57928</v>
       </c>
       <c r="D14">
-        <v>0.36495</v>
+        <v>0.36478</v>
       </c>
       <c r="E14">
         <v>0.00427</v>
@@ -1978,7 +1978,7 @@
         <v>0</v>
       </c>
       <c r="L14">
-        <v>0.03399</v>
+        <v>0.03397</v>
       </c>
       <c r="M14">
         <v>0</v>
@@ -2041,16 +2041,16 @@
         </is>
       </c>
       <c r="C16">
-        <v>0.39476</v>
+        <v>0.39534</v>
       </c>
       <c r="D16">
-        <v>0.00019</v>
+        <v>0</v>
       </c>
       <c r="E16">
-        <v>0.5096000000000001</v>
+        <v>0.50972</v>
       </c>
       <c r="F16">
-        <v>0.06863</v>
+        <v>0.06822</v>
       </c>
       <c r="G16">
         <v>0</v>
@@ -2065,7 +2065,7 @@
         <v>0</v>
       </c>
       <c r="K16">
-        <v>0.02682</v>
+        <v>0.02672</v>
       </c>
       <c r="L16">
         <v>0</v>
@@ -2221,13 +2221,13 @@
         </is>
       </c>
       <c r="C20">
-        <v>0.71454</v>
+        <v>0.7139</v>
       </c>
       <c r="D20">
         <v>0</v>
       </c>
       <c r="E20">
-        <v>0.02935</v>
+        <v>0.02933</v>
       </c>
       <c r="F20">
         <v>0</v>
@@ -2245,13 +2245,13 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0.20995</v>
+        <v>0.21066</v>
       </c>
       <c r="L20">
         <v>0</v>
       </c>
       <c r="M20">
-        <v>0.04616</v>
+        <v>0.04612</v>
       </c>
     </row>
     <row r="21">
